--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 31,08,26 бррсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 31,08,26 бррсч ост зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973C0B11-8F9B-4DF0-B8CB-A56FF2747155}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C11A543-9880-4A9F-9E8A-B70904CE10FB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="49">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -172,6 +169,12 @@
   </si>
   <si>
     <t>7216 СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>08,09,</t>
   </si>
 </sst>
 </file>
@@ -759,46 +762,46 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
@@ -836,40 +839,42 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="1"/>
+      <c r="Q4" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="AB4" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
@@ -936,7 +941,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -979,7 +984,7 @@
       <c r="AC5" s="1"/>
       <c r="AD5" s="4">
         <f>SUM(AD6:AD500)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
@@ -1003,10 +1008,10 @@
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C6" s="1">
         <v>240</v>
@@ -1023,7 +1028,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1075,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="AC6" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AD6" s="1">
-        <f>G6*Q6</f>
+        <f t="shared" ref="AD6:AD16" si="3">G6*Q6</f>
         <v>0</v>
       </c>
       <c r="AE6" s="1"/>
@@ -1103,10 +1108,10 @@
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C7" s="1">
         <v>96.688000000000002</v>
@@ -1123,7 +1128,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1135,16 +1140,16 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1">
-        <f t="shared" ref="P7:P16" si="3">E7/5</f>
+        <f t="shared" ref="P7:P16" si="4">E7/5</f>
         <v>0</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="1" t="e">
-        <f t="shared" ref="R7:R16" si="4">(F7+O7+Q7)/P7</f>
+        <f t="shared" ref="R7:R16" si="5">(F7+O7+Q7)/P7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="S7" s="1" t="e">
-        <f t="shared" ref="S7:S16" si="5">(F7+O7)/P7</f>
+        <f t="shared" ref="S7:S16" si="6">(F7+O7)/P7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="T7" s="1">
@@ -1175,10 +1180,10 @@
         <v>0.91959999999999997</v>
       </c>
       <c r="AC7" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AD7" s="1">
-        <f>G7*Q7</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE7" s="1"/>
@@ -1203,10 +1208,10 @@
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1">
         <v>331.21</v>
@@ -1225,7 +1230,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
@@ -1239,18 +1244,18 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="1">
-        <f t="shared" si="4"/>
-        <v>1651.0499999999997</v>
-      </c>
-      <c r="S8" s="1">
         <f t="shared" si="5"/>
         <v>1651.0499999999997</v>
       </c>
+      <c r="S8" s="1">
+        <f t="shared" si="6"/>
+        <v>1651.0499999999997</v>
+      </c>
       <c r="T8" s="1">
         <v>1.8408</v>
       </c>
@@ -1279,10 +1284,10 @@
         <v>0</v>
       </c>
       <c r="AC8" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AD8" s="1">
-        <f>G8*Q8</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE8" s="1"/>
@@ -1307,10 +1312,10 @@
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1">
         <v>107</v>
@@ -1329,7 +1334,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
@@ -1343,18 +1348,18 @@
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="1">
-        <f t="shared" si="4"/>
-        <v>84.166666666666671</v>
-      </c>
-      <c r="S9" s="1">
         <f t="shared" si="5"/>
         <v>84.166666666666671</v>
       </c>
+      <c r="S9" s="1">
+        <f t="shared" si="6"/>
+        <v>84.166666666666671</v>
+      </c>
       <c r="T9" s="1">
         <v>0</v>
       </c>
@@ -1383,10 +1388,10 @@
         <v>1.4</v>
       </c>
       <c r="AC9" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AD9" s="1">
-        <f>G9*Q9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE9" s="1"/>
@@ -1411,10 +1416,10 @@
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1">
         <v>202</v>
@@ -1433,7 +1438,7 @@
         <v>120</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1449,19 +1454,18 @@
         <v>30</v>
       </c>
       <c r="P10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13</v>
       </c>
       <c r="Q10" s="5">
-        <f>15*P10-O10-F10</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" si="4"/>
-        <v>15</v>
+        <f t="shared" si="5"/>
+        <v>15.153846153846153</v>
       </c>
       <c r="S10" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12.846153846153847</v>
       </c>
       <c r="T10" s="1">
@@ -1493,8 +1497,8 @@
       </c>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1">
-        <f>G10*Q10</f>
-        <v>8.4</v>
+        <f t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="AE10" s="1"/>
       <c r="AF10" s="1"/>
@@ -1518,10 +1522,10 @@
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1">
         <v>182</v>
@@ -1540,7 +1544,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1554,18 +1558,18 @@
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="1">
-        <f t="shared" si="4"/>
-        <v>15.222222222222221</v>
-      </c>
-      <c r="S11" s="1">
         <f t="shared" si="5"/>
         <v>15.222222222222221</v>
       </c>
+      <c r="S11" s="1">
+        <f t="shared" si="6"/>
+        <v>15.222222222222221</v>
+      </c>
       <c r="T11" s="1">
         <v>10.6</v>
       </c>
@@ -1595,7 +1599,7 @@
       </c>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1">
-        <f>G11*Q11</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE11" s="1"/>
@@ -1620,10 +1624,10 @@
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
         <v>208</v>
@@ -1644,7 +1648,7 @@
         <v>120</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1660,19 +1664,18 @@
         <v>80</v>
       </c>
       <c r="P12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>16.2</v>
       </c>
       <c r="Q12" s="5">
-        <f t="shared" ref="Q11:Q16" si="6">15*P12-O12-F12</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R12" s="1">
-        <f t="shared" si="4"/>
-        <v>15</v>
+        <f t="shared" si="5"/>
+        <v>15.246913580246915</v>
       </c>
       <c r="S12" s="1">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>12.777777777777779</v>
       </c>
       <c r="T12" s="1">
@@ -1704,8 +1707,8 @@
       </c>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1">
-        <f>G12*Q12</f>
-        <v>12.6</v>
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
@@ -1729,10 +1732,10 @@
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1">
         <v>65</v>
@@ -1753,7 +1756,7 @@
         <v>120</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1769,18 +1772,18 @@
         <v>60</v>
       </c>
       <c r="P13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.2</v>
       </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="1">
-        <f t="shared" si="4"/>
-        <v>24.761904761904759</v>
-      </c>
-      <c r="S13" s="1">
         <f t="shared" si="5"/>
         <v>24.761904761904759</v>
       </c>
+      <c r="S13" s="1">
+        <f t="shared" si="6"/>
+        <v>24.761904761904759</v>
+      </c>
       <c r="T13" s="1">
         <v>8.1999999999999993</v>
       </c>
@@ -1810,7 +1813,7 @@
       </c>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1">
-        <f>G13*Q13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE13" s="1"/>
@@ -1835,10 +1838,10 @@
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1">
         <v>51</v>
@@ -1859,7 +1862,7 @@
         <v>120</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1875,18 +1878,18 @@
         <v>210</v>
       </c>
       <c r="P14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="1">
-        <f t="shared" si="4"/>
-        <v>61.6</v>
-      </c>
-      <c r="S14" s="1">
         <f t="shared" si="5"/>
         <v>61.6</v>
       </c>
+      <c r="S14" s="1">
+        <f t="shared" si="6"/>
+        <v>61.6</v>
+      </c>
       <c r="T14" s="1">
         <v>22</v>
       </c>
@@ -1916,7 +1919,7 @@
       </c>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1">
-        <f>G14*Q14</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE14" s="1"/>
@@ -1941,10 +1944,10 @@
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1">
         <v>103</v>
@@ -1961,7 +1964,7 @@
         <v>120</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1973,18 +1976,18 @@
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="1" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S15" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="S15" s="1" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T15" s="1">
         <v>0</v>
       </c>
@@ -2013,10 +2016,10 @@
         <v>1</v>
       </c>
       <c r="AC15" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AD15" s="1">
-        <f>G15*Q15</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE15" s="1"/>
@@ -2041,10 +2044,10 @@
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1">
         <v>268</v>
@@ -2065,7 +2068,7 @@
         <v>180</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -2079,18 +2082,18 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>13.6</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="1">
-        <f t="shared" si="4"/>
-        <v>14.705882352941178</v>
-      </c>
-      <c r="S16" s="1">
         <f t="shared" si="5"/>
         <v>14.705882352941178</v>
       </c>
+      <c r="S16" s="1">
+        <f t="shared" si="6"/>
+        <v>14.705882352941178</v>
+      </c>
       <c r="T16" s="1">
         <v>6.6</v>
       </c>
@@ -2120,7 +2123,7 @@
       </c>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1">
-        <f>G16*Q16</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AE16" s="1"/>
